--- a/data/trans_camb/P43B-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P43B-Edad-trans_camb.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21,92</t>
+          <t>21,66</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21,92</t>
+          <t>21,66</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 42,21</t>
+          <t>-14,94; 39,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 54,27</t>
+          <t>-11,02; 53,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 42,21</t>
+          <t>-14,94; 39,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 54,27</t>
+          <t>-11,02; 53,86</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>122,01%</t>
+          <t>120,55%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>122,01%</t>
+          <t>120,55%</t>
         </is>
       </c>
     </row>
@@ -657,22 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-63,17; 651,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-61,97; 783,74</t>
+          <t>-55,34; 944,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-63,17; 651,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-61,97; 783,74</t>
+          <t>-55,34; 944,26</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-2,89</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-2,89</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 9,19</t>
+          <t>-19,25; 10,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 17,21</t>
+          <t>-17,44; 14,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 9,19</t>
+          <t>-19,25; 10,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 17,21</t>
+          <t>-17,44; 14,82</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-3,52%</t>
+          <t>-8,96%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,52%</t>
+          <t>-8,96%</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,06; 37,08</t>
+          <t>-49,06; 46,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,7; 71,63</t>
+          <t>-46,5; 62,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,06; 37,08</t>
+          <t>-49,06; 46,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,7; 71,63</t>
+          <t>-46,5; 62,02</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>4,83</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>4,83</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 4,89</t>
+          <t>-13,45; 4,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 12,82</t>
+          <t>-3,8; 14,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 4,89</t>
+          <t>-13,45; 4,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 12,82</t>
+          <t>-3,8; 14,1</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -889,22 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,96; 19,11</t>
+          <t>-38,62; 19,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 50,6</t>
+          <t>-11,81; 54,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,96; 19,11</t>
+          <t>-38,62; 19,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 50,6</t>
+          <t>-11,81; 54,3</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8,77</t>
+          <t>11,91</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,77</t>
+          <t>11,91</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 4,27</t>
+          <t>-7,22; 3,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 14,95</t>
+          <t>5,9; 17,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 4,27</t>
+          <t>-7,22; 3,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 14,95</t>
+          <t>5,9; 17,91</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>66,32%</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-35,71; 30,56</t>
+          <t>-34,35; 28,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 96,76</t>
+          <t>27,29; 120,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,71; 30,56</t>
+          <t>-34,35; 28,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 96,76</t>
+          <t>27,29; 120,23</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4,87</t>
+          <t>5,02</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,87</t>
+          <t>5,02</t>
         </is>
       </c>
     </row>
@@ -1065,22 +1065,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 3,74</t>
+          <t>-4,65; 3,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 8,67</t>
+          <t>0,99; 8,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 3,74</t>
+          <t>-4,65; 3,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 8,67</t>
+          <t>0,99; 8,73</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>61,86%</t>
         </is>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-42,96; 63,76</t>
+          <t>-44,54; 73,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7,14; 154,34</t>
+          <t>5,41; 144,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,96; 63,76</t>
+          <t>-44,54; 73,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7,14; 154,34</t>
+          <t>5,41; 144,48</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>4,64</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>4,64</t>
         </is>
       </c>
     </row>
@@ -1181,22 +1181,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 4,43</t>
+          <t>-4,44; 4,3</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 5,47</t>
+          <t>0,69; 8,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 4,43</t>
+          <t>-4,44; 4,3</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 5,47</t>
+          <t>0,69; 8,5</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-3,89%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-3,89%</t>
+          <t>72,07%</t>
         </is>
       </c>
     </row>
@@ -1237,22 +1237,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-46,12; 109,5</t>
+          <t>-52,06; 95,27</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-73,41; 97,49</t>
+          <t>5,92; 202,82</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-46,12; 109,5</t>
+          <t>-52,06; 95,27</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-73,41; 97,49</t>
+          <t>5,92; 202,82</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2,55</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2,55</t>
+          <t>2,54</t>
         </is>
       </c>
     </row>
@@ -1297,22 +1297,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 2,29</t>
+          <t>-6,18; 2,48</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 6,37</t>
+          <t>-1,86; 6,3</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 2,29</t>
+          <t>-6,18; 2,48</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 6,37</t>
+          <t>-1,86; 6,3</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -1353,22 +1353,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-88,19; 96,11</t>
+          <t>-81,25; 93,19</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-20,98; 230,75</t>
+          <t>-24,32; 205,52</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-88,19; 96,11</t>
+          <t>-81,25; 93,19</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-20,98; 230,75</t>
+          <t>-24,32; 205,52</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>4,14</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>4,14</t>
         </is>
       </c>
     </row>
@@ -1413,22 +1413,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 0,6</t>
+          <t>-4,43; 0,5</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 4,47</t>
+          <t>1,33; 6,55</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 0,6</t>
+          <t>-4,43; 0,5</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 4,47</t>
+          <t>1,33; 6,55</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -1469,22 +1469,22 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 4,37</t>
+          <t>-27,64; 4,05</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 32,78</t>
+          <t>8,11; 50,54</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 4,37</t>
+          <t>-27,64; 4,05</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 32,78</t>
+          <t>8,11; 50,54</t>
         </is>
       </c>
     </row>
